--- a/output/casestudy_20260830.xlsx
+++ b/output/casestudy_20260830.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>23.10109049989842</v>
+        <v>20.97248550015502</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20.5417283999268</v>
+        <v>20.82720520021394</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.35255469987169</v>
+        <v>12.51805300009437</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.86513339984231</v>
+        <v>21.62621870008297</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22.90771569986828</v>
+        <v>23.47953789983876</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>14.80253869993612</v>
+        <v>14.91605970007367</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.1 초</t>
+          <t>21.0 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.5 초</t>
+          <t>20.8 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.4 초</t>
+          <t>12.5 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.9 초</t>
+          <t>21.6 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.9 초</t>
+          <t>23.5 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.8 초</t>
+          <t>14.9 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>117.8 초</t>
+          <t>116.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260830.xlsx
+++ b/output/casestudy_20260830.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>20.97248550015502</v>
+        <v>21.53990130010061</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20.82720520021394</v>
+        <v>21.26380189997144</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.51805300009437</v>
+        <v>12.48406279995106</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.62621870008297</v>
+        <v>22.85263039986603</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>23.47953789983876</v>
+        <v>24.92579240002669</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>14.91605970007367</v>
+        <v>15.68457849998958</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.0 초</t>
+          <t>21.5 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.8 초</t>
+          <t>21.3 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.6 초</t>
+          <t>22.9 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23.5 초</t>
+          <t>24.9 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.9 초</t>
+          <t>15.7 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>116.3 초</t>
+          <t>120.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260830.xlsx
+++ b/output/casestudy_20260830.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>21.53990130010061</v>
+        <v>21.19972339994274</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>21.26380189997144</v>
+        <v>21.18370799999684</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.48406279995106</v>
+        <v>12.61166370008141</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22.85263039986603</v>
+        <v>22.14514719997533</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24.92579240002669</v>
+        <v>26.22687310003676</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>15.68457849998958</v>
+        <v>15.35979479993694</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.5 초</t>
+          <t>21.2 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.3 초</t>
+          <t>21.2 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.5 초</t>
+          <t>12.6 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.9 초</t>
+          <t>22.1 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.9 초</t>
+          <t>26.2 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.7 초</t>
+          <t>15.4 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>120.9 초</t>
+          <t>120.7 초</t>
         </is>
       </c>
     </row>
